--- a/result/SSE Results.xlsx
+++ b/result/SSE Results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="47">
   <si>
     <t>w/ additional activation (s=2.0)</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Annotation</t>
   </si>
   <si>
-    <t xml:space="preserve">Combine : Fused scales in scale channels, Isolate : One scale in each scale dimensions </t>
+    <t xml:space="preserve">Combine: Fused scales in scale dimensions, Isolate : One scale in each scale dimensions </t>
   </si>
   <si>
     <t>(P) : Pure disco basis</t>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>Isolate(w/ nms, AUC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combine: Fused scales in scale channels, Isolate : One scale in each scale dimensions </t>
   </si>
   <si>
     <t>Disco basis combined with 2D hermite gaussian</t>
@@ -5668,13 +5665,13 @@
     </row>
     <row r="38">
       <c r="A38" s="56" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="F38" s="5"/>
     </row>
     <row r="39">
       <c r="A39" s="58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -5695,7 +5692,7 @@
     </row>
     <row r="42">
       <c r="A42" s="106" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E42" s="27"/>
       <c r="F42" s="27"/>
